--- a/docs/nekt/inventario-contas-1743-2026-10-13.xlsx
+++ b/docs/nekt/inventario-contas-1743-2026-10-13.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Premissas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contas'!$A$1:$U$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cronograma'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contas'!$A$1:$U$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cronograma'!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -574,10 +574,14 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Não precisa manter (a validar)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -601,6 +605,9 @@
         <v>8</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>111</v>
       </c>
     </row>
@@ -626,38 +633,44 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LinkedIn Ads</t>
+          <t>TikTok Ads</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -676,13 +689,16 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spotify Ads</t>
+          <t>LinkedIn Ads</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -695,19 +711,22 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Twitter/X Ads</t>
+          <t>Spotify Ads</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -726,134 +745,184 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Twitter/X Ads</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B11" s="4">
-        <f>SUM(B5:B10)</f>
+      <c r="B12" s="4">
+        <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="C11" s="4">
-        <f>SUM(C5:C10)</f>
+      <c r="C12" s="4">
+        <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D11" s="4">
-        <f>SUM(D5:D10)</f>
+      <c r="D12" s="4">
+        <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E11" s="4">
-        <f>SUM(E5:E10)</f>
+      <c r="E12" s="4">
+        <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F11" s="4">
-        <f>SUM(F5:F10)</f>
+      <c r="F12" s="4">
+        <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G11" s="4">
-        <f>SUM(G5:G10)</f>
+      <c r="G12" s="4">
+        <f>SUM(G5:G11)</f>
         <v/>
       </c>
-      <c r="H11" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="H12" s="4">
+        <f>SUM(H5:H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>LEITURA RÁPIDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>• Meta Ads: 7 contas conectadas e extraindo. 92 rascunhos criados (84 aguardam OAuth; 8 do Termo ainda não aparecem no MCC Meta, então a autorização pode falhar até a Meta concluir a atribuição). 4 contas bloqueadas (1 fonte arquivada em 03/09 por perda de permissão + 3 contas desabilitadas na Meta).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>• Google Ads: 40 contas dos documentos já têm fonte e extraem (2 delas sem dado útil). 12 rascunhos aguardam OAuth do administrador do MCC. Bloqueios: Prestex (OzfZ), Santo Remédio (AMd2, conta saiu do MCC) e Comac e Braga Venda Direta (IDs do Doc 2 que não aparecem no MCC).</t>
+          <t>• Meta Ads: 7 contas conectadas e extraindo. 92 rascunhos criados (84 aguardam OAuth; 8 do Termo ainda não aparecem no MCC Meta, então a autorização pode falhar até a Meta concluir a atribuição). 4 contas bloqueadas (1 fonte arquivada em 03/09 por perda de permissão + 3 contas desabilitadas na Meta).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>• Grupo Nova Era: fora do escopo ativo (instrução da tarefa). Nenhuma conta Nova Era é integrada; as 5 contas de Google Ads dela continuam vinculadas ao MCC e gastando e precisam ser desvinculadas pelo administrador.</t>
+          <t>• Google Ads: 40 contas dos documentos já têm fonte e extraem (2 delas sem dado útil). 12 rascunhos aguardam OAuth do administrador do MCC. Bloqueios: Prestex (OzfZ), Santo Remédio (AMd2, conta saiu do MCC) e Comac e Braga Venda Direta (IDs do Doc 2 que não aparecem no MCC).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>• TikTok, LinkedIn, Spotify e X: aparecem na planilha de squad sem ID de conta; existem conectores Nekt de TikTok Ads e LinkedIn Ads, mas nenhuma fonte foi criada. Spotify e X não têm conector.</t>
+          <t>• RD Station: 34 fontes publicadas (a planilha Inbound lista 51 clientes com plano RD). 30 extraem todo dia; 1 roda sem entregar dado (AMZ Imports); 1 está bloqueada (CDL, 403); 2 são cópias da conta da Vanguarda. 24 clientes da planilha Inbound não têm fonte RD na Nekt, alguns podem já estar sob outra fonte (Braga, Pneu Forte, PMZ Escola) e precisam de validação antes de criar rascunho. Das 30 fontes que entregam, só 8 trazem o cadastro completo do contato; as outras 22 trazem o grão mínimo (id, e-mail e última conversão).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>• Grupo Nova Era: fora do escopo ativo (instrução da tarefa). Nenhuma conta Nova Era é integrada; as 5 contas de Google Ads dela continuam vinculadas ao MCC e gastando e precisam ser desvinculadas pelo administrador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>• TikTok, LinkedIn, Spotify e X: aparecem na planilha de squad sem ID de conta; existem conectores Nekt de TikTok Ads e LinkedIn Ads, mas nenhuma fonte foi criada. Spotify e X não têm conector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>• Reautorização do conector Google Ads v2.53 vale para todas as fontes de Google Ads da Nekt, com prazo 23/10/2026.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>DEPENDÊNCIAS QUE DESTRAVAM O RESTANTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>1) Administrador do MCC Google Ads (1704439246): autorizar 12 rascunhos + reautenticar Prestex + reautorizar v2.53 + desvincular Nova Era.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2) Administrador do Business Manager Meta: concluir a atribuição do Termo (8 contas) e autorizar o OAuth dos rascunhos Meta com usuário que tenha as contas.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>3) Suporte da Nekt: restaurar as 4 fontes Meta arquivadas em 03/09 (somente as que continuam no escopo; Nova Era permanece arquivada).</t>
+          <t>1) Administrador do MCC Google Ads (1704439246): autorizar 12 rascunhos + reautenticar Prestex + reautorizar v2.53 + desvincular Nova Era.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>4) Alinhamento do escopo com os AMs: confirmar contas candidatas a encerrar e clientes que não constam na divisão por squad.</t>
+          <t>2) Administrador do Business Manager Meta: concluir a atribuição do Termo (8 contas) e autorizar o OAuth dos rascunhos Meta com usuário que tenha as contas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3) Suporte da Nekt: restaurar as 4 fontes Meta arquivadas em 03/09 (somente as que continuam no escopo; Nova Era permanece arquivada).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>4) Analistas Inbound (Joyce, Juan Carlos e Bryan): validar a cobertura das 24 contas RD sem fonte e autorizar o OAuth com o administrador da conta RD de cada cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>5) Alinhamento do escopo com os AMs: confirmar contas candidatas a encerrar e clientes que não constam na divisão por squad.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
@@ -867,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U183"/>
+  <dimension ref="A1:U241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17121,12 +17190,12 @@
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>Spotify Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>PÁTIO GOURMET (LOJAS)</t>
+          <t>ARENA TINTAS</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
@@ -17136,12 +17205,12 @@
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>conta não informada nos documentos</t>
+          <t>(sem fonte)</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>Planilha de divisão por squad</t>
+          <t>Planilha Inbound (plano RD)</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
@@ -17151,19 +17220,19 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Plano PRO</t>
         </is>
       </c>
       <c r="H178" s="9" t="n"/>
       <c r="I178" s="7" t="inlineStr"/>
-      <c r="J178" s="14" t="inlineStr">
-        <is>
-          <t>Sem conexão</t>
+      <c r="J178" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K178" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão — não há conector Nekt para esta plataforma</t>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
         </is>
       </c>
       <c r="L178" s="7" t="inlineStr">
@@ -17173,30 +17242,34 @@
       </c>
       <c r="M178" s="7" t="inlineStr">
         <is>
-          <t>ID da conta não consta em nenhum documento</t>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
         </is>
       </c>
       <c r="N178" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="O178" s="7" t="inlineStr"/>
       <c r="P178" s="7" t="inlineStr">
         <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
-      <c r="Q178" s="7" t="inlineStr"/>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q178" s="7" t="inlineStr">
+        <is>
+          <t>Fabiane Carvalho</t>
+        </is>
+      </c>
       <c r="R178" s="7" t="inlineStr"/>
       <c r="S178" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="T178" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="U178" s="7" t="inlineStr"/>
@@ -17204,12 +17277,12 @@
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>BA ELÉTRICA</t>
+          <t>BAJAJ</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
@@ -17219,12 +17292,12 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>conta não informada nos documentos</t>
+          <t>(sem fonte)</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>Planilha de divisão por squad</t>
+          <t>Planilha Inbound (plano RD)</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
@@ -17234,19 +17307,19 @@
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Plano PRO</t>
         </is>
       </c>
       <c r="H179" s="9" t="n"/>
       <c r="I179" s="7" t="inlineStr"/>
-      <c r="J179" s="14" t="inlineStr">
-        <is>
-          <t>Sem conexão</t>
+      <c r="J179" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K179" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
         </is>
       </c>
       <c r="L179" s="7" t="inlineStr">
@@ -17256,42 +17329,34 @@
       </c>
       <c r="M179" s="7" t="inlineStr">
         <is>
-          <t>ID da conta não consta em nenhum documento</t>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
         </is>
       </c>
       <c r="N179" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
-        </is>
-      </c>
-      <c r="O179" s="7" t="inlineStr">
-        <is>
-          <t>Gabrielly</t>
-        </is>
-      </c>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O179" s="7" t="inlineStr"/>
       <c r="P179" s="7" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Juan Carlos</t>
         </is>
       </c>
       <c r="Q179" s="7" t="inlineStr">
         <is>
-          <t>Fabiane Carvalho</t>
-        </is>
-      </c>
-      <c r="R179" s="7" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
+          <t>Fernanda Bonates</t>
+        </is>
+      </c>
+      <c r="R179" s="7" t="inlineStr"/>
       <c r="S179" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="T179" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="U179" s="7" t="inlineStr"/>
@@ -17299,12 +17364,12 @@
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>PÁTIO GOURMET (LOJAS)</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
@@ -17314,12 +17379,12 @@
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>conta não informada nos documentos</t>
+          <t>(sem fonte)</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>Planilha de divisão por squad</t>
+          <t>Planilha Inbound (plano RD)</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
@@ -17329,19 +17394,19 @@
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Plano LIGHT</t>
         </is>
       </c>
       <c r="H180" s="9" t="n"/>
       <c r="I180" s="7" t="inlineStr"/>
-      <c r="J180" s="14" t="inlineStr">
-        <is>
-          <t>Sem conexão</t>
+      <c r="J180" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K180" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
         </is>
       </c>
       <c r="L180" s="7" t="inlineStr">
@@ -17351,30 +17416,30 @@
       </c>
       <c r="M180" s="7" t="inlineStr">
         <is>
-          <t>ID da conta não consta em nenhum documento</t>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
         </is>
       </c>
       <c r="N180" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="O180" s="7" t="inlineStr"/>
       <c r="P180" s="7" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Juan Carlos</t>
         </is>
       </c>
       <c r="Q180" s="7" t="inlineStr"/>
       <c r="R180" s="7" t="inlineStr"/>
       <c r="S180" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="T180" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="U180" s="7" t="inlineStr"/>
@@ -17382,12 +17447,12 @@
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>SANTO REMÉDIO</t>
+          <t>BRAGA MOTOS - YAMAHA - PÓS VENDAS</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
@@ -17397,12 +17462,12 @@
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>conta não informada nos documentos</t>
+          <t>(sem fonte)</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>Planilha de divisão por squad</t>
+          <t>Planilha Inbound (plano RD)</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -17412,19 +17477,19 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Plano PRO</t>
         </is>
       </c>
       <c r="H181" s="9" t="n"/>
       <c r="I181" s="7" t="inlineStr"/>
-      <c r="J181" s="14" t="inlineStr">
-        <is>
-          <t>Sem conexão</t>
+      <c r="J181" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K181" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
         </is>
       </c>
       <c r="L181" s="7" t="inlineStr">
@@ -17434,55 +17499,51 @@
       </c>
       <c r="M181" s="7" t="inlineStr">
         <is>
-          <t>ID da conta não consta em nenhum documento</t>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte idF7 ou WHAa</t>
         </is>
       </c>
       <c r="N181" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
-        </is>
-      </c>
-      <c r="O181" s="7" t="inlineStr">
-        <is>
-          <t>Wilkefor</t>
-        </is>
-      </c>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O181" s="7" t="inlineStr"/>
       <c r="P181" s="7" t="inlineStr">
         <is>
-          <t>Wilkefor</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="Q181" s="7" t="inlineStr">
         <is>
-          <t>Silvia Calderaro</t>
-        </is>
-      </c>
-      <c r="R181" s="7" t="inlineStr">
-        <is>
-          <t>Ativo</t>
-        </is>
-      </c>
+          <t>Ana Júlia</t>
+        </is>
+      </c>
+      <c r="R181" s="7" t="inlineStr"/>
       <c r="S181" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="T181" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="U181" s="7" t="inlineStr"/>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U181" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>TUBOAÇOS</t>
+          <t>BRAGA MOTOS - YAMAHA - VENDAS</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
@@ -17492,12 +17553,12 @@
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>conta não informada nos documentos</t>
+          <t>(sem fonte)</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>Planilha de divisão por squad</t>
+          <t>Planilha Inbound (plano RD)</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
@@ -17507,19 +17568,19 @@
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Plano PRO</t>
         </is>
       </c>
       <c r="H182" s="9" t="n"/>
       <c r="I182" s="7" t="inlineStr"/>
-      <c r="J182" s="14" t="inlineStr">
-        <is>
-          <t>Sem conexão</t>
+      <c r="J182" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K182" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
         </is>
       </c>
       <c r="L182" s="7" t="inlineStr">
@@ -17529,43 +17590,51 @@
       </c>
       <c r="M182" s="7" t="inlineStr">
         <is>
-          <t>ID da conta não consta em nenhum documento</t>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte idF7 ou WHAa</t>
         </is>
       </c>
       <c r="N182" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="O182" s="7" t="inlineStr"/>
       <c r="P182" s="7" t="inlineStr">
         <is>
-          <t>Bruno</t>
-        </is>
-      </c>
-      <c r="Q182" s="7" t="inlineStr"/>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q182" s="7" t="inlineStr">
+        <is>
+          <t>Ana Júlia</t>
+        </is>
+      </c>
       <c r="R182" s="7" t="inlineStr"/>
       <c r="S182" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="T182" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="U182" s="7" t="inlineStr"/>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U182" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>Twitter/X Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>PÁTIO GOURMET (LOJAS)</t>
+          <t>BRAGA VEÍCULOS - VENDA DIRETA</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
@@ -17575,12 +17644,12 @@
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>conta não informada nos documentos</t>
+          <t>(sem fonte)</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>Planilha de divisão por squad</t>
+          <t>Planilha Inbound (plano RD)</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
@@ -17590,19 +17659,19 @@
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Plano PRO</t>
         </is>
       </c>
       <c r="H183" s="9" t="n"/>
       <c r="I183" s="7" t="inlineStr"/>
-      <c r="J183" s="14" t="inlineStr">
-        <is>
-          <t>Sem conexão</t>
+      <c r="J183" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="K183" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão — não há conector Nekt para esta plataforma</t>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
         </is>
       </c>
       <c r="L183" s="7" t="inlineStr">
@@ -17612,36 +17681,5026 @@
       </c>
       <c r="M183" s="7" t="inlineStr">
         <is>
-          <t>ID da conta não consta em nenhum documento</t>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte WHAa</t>
         </is>
       </c>
       <c r="N183" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="O183" s="7" t="inlineStr"/>
       <c r="P183" s="7" t="inlineStr">
         <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
-      <c r="Q183" s="7" t="inlineStr"/>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q183" s="7" t="inlineStr">
+        <is>
+          <t>Igor Luís</t>
+        </is>
+      </c>
       <c r="R183" s="7" t="inlineStr"/>
       <c r="S183" s="7" t="inlineStr">
         <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T183" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U183" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>BRAGA VEÍCULOS VAREJO</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H184" s="9" t="n"/>
+      <c r="I184" s="7" t="inlineStr"/>
+      <c r="J184" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K184" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
+        </is>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M184" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte WHAa</t>
+        </is>
+      </c>
+      <c r="N184" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O184" s="7" t="inlineStr"/>
+      <c r="P184" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q184" s="7" t="inlineStr">
+        <is>
+          <t>Igor Luís</t>
+        </is>
+      </c>
+      <c r="R184" s="7" t="inlineStr"/>
+      <c r="S184" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T184" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U184" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>BRAGA VEÍCULOS VENDAS - PÓS VENDA</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="n"/>
+      <c r="I185" s="7" t="inlineStr"/>
+      <c r="J185" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K185" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
+        </is>
+      </c>
+      <c r="L185" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M185" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte WHAa</t>
+        </is>
+      </c>
+      <c r="N185" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O185" s="7" t="inlineStr"/>
+      <c r="P185" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q185" s="7" t="inlineStr">
+        <is>
+          <t>Igor Luís</t>
+        </is>
+      </c>
+      <c r="R185" s="7" t="inlineStr"/>
+      <c r="S185" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T185" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U185" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>CAA ALUMÍNIO</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H186" s="9" t="n"/>
+      <c r="I186" s="7" t="inlineStr"/>
+      <c r="J186" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K186" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L186" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M186" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N186" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O186" s="7" t="inlineStr"/>
+      <c r="P186" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q186" s="7" t="inlineStr">
+        <is>
+          <t>Fernanda Bonates</t>
+        </is>
+      </c>
+      <c r="R186" s="7" t="inlineStr"/>
+      <c r="S186" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T186" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U186" s="7" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>CAA TINTAS</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H187" s="9" t="n"/>
+      <c r="I187" s="7" t="inlineStr"/>
+      <c r="J187" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K187" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L187" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M187" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N187" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O187" s="7" t="inlineStr"/>
+      <c r="P187" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q187" s="7" t="inlineStr">
+        <is>
+          <t>Fabiane Carvalho</t>
+        </is>
+      </c>
+      <c r="R187" s="7" t="inlineStr"/>
+      <c r="S187" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T187" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>CHARÃO</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H188" s="9" t="n"/>
+      <c r="I188" s="7" t="inlineStr"/>
+      <c r="J188" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K188" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L188" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M188" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N188" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O188" s="7" t="inlineStr"/>
+      <c r="P188" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q188" s="7" t="inlineStr"/>
+      <c r="R188" s="7" t="inlineStr"/>
+      <c r="S188" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T188" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U188" s="7" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>CONSTROI INCORPORADORA</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H189" s="9" t="n"/>
+      <c r="I189" s="7" t="inlineStr"/>
+      <c r="J189" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K189" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M189" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N189" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O189" s="7" t="inlineStr"/>
+      <c r="P189" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q189" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R189" s="7" t="inlineStr"/>
+      <c r="S189" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T189" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U189" s="7" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PNEU FORTE</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H190" s="9" t="n"/>
+      <c r="I190" s="7" t="inlineStr"/>
+      <c r="J190" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K190" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
+        </is>
+      </c>
+      <c r="L190" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M190" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte 7K57</t>
+        </is>
+      </c>
+      <c r="N190" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O190" s="7" t="inlineStr"/>
+      <c r="P190" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q190" s="7" t="inlineStr">
+        <is>
+          <t>Yanka Gabriela</t>
+        </is>
+      </c>
+      <c r="R190" s="7" t="inlineStr"/>
+      <c r="S190" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T190" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U190" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>DOCTOR MAIS SAÚDE</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H191" s="9" t="n"/>
+      <c r="I191" s="7" t="inlineStr"/>
+      <c r="J191" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K191" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M191" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N191" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O191" s="7" t="inlineStr"/>
+      <c r="P191" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q191" s="7" t="inlineStr">
+        <is>
+          <t>Ana Júlia</t>
+        </is>
+      </c>
+      <c r="R191" s="7" t="inlineStr"/>
+      <c r="S191" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T191" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U191" s="7" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>HAGE ALIMENTOS</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H192" s="9" t="n"/>
+      <c r="I192" s="7" t="inlineStr"/>
+      <c r="J192" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K192" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L192" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M192" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N192" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O192" s="7" t="inlineStr"/>
+      <c r="P192" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q192" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R192" s="7" t="inlineStr"/>
+      <c r="S192" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T192" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U192" s="7" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>LEGACY PNEUS</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>Plano BASIC</t>
+        </is>
+      </c>
+      <c r="H193" s="9" t="n"/>
+      <c r="I193" s="7" t="inlineStr"/>
+      <c r="J193" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K193" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L193" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M193" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N193" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O193" s="7" t="inlineStr"/>
+      <c r="P193" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q193" s="7" t="inlineStr"/>
+      <c r="R193" s="7" t="inlineStr"/>
+      <c r="S193" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T193" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U193" s="7" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>LOVOL</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>Plano (não informado)</t>
+        </is>
+      </c>
+      <c r="H194" s="9" t="n"/>
+      <c r="I194" s="7" t="inlineStr"/>
+      <c r="J194" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K194" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M194" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N194" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O194" s="7" t="inlineStr"/>
+      <c r="P194" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q194" s="7" t="inlineStr"/>
+      <c r="R194" s="7" t="inlineStr"/>
+      <c r="S194" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T194" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U194" s="7" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>PMZ ESCOLA</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H195" s="9" t="n"/>
+      <c r="I195" s="7" t="inlineStr"/>
+      <c r="J195" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K195" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
+        </is>
+      </c>
+      <c r="L195" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M195" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte bdVN</t>
+        </is>
+      </c>
+      <c r="N195" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O195" s="7" t="inlineStr"/>
+      <c r="P195" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q195" s="7" t="inlineStr">
+        <is>
+          <t>Igor Luís</t>
+        </is>
+      </c>
+      <c r="R195" s="7" t="inlineStr"/>
+      <c r="S195" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T195" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U195" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>RODRIX</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H196" s="9" t="n"/>
+      <c r="I196" s="7" t="inlineStr"/>
+      <c r="J196" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K196" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L196" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M196" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N196" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O196" s="7" t="inlineStr"/>
+      <c r="P196" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q196" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R196" s="7" t="inlineStr"/>
+      <c r="S196" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T196" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U196" s="7" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>ROYAL ENFIELD</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H197" s="9" t="n"/>
+      <c r="I197" s="7" t="inlineStr"/>
+      <c r="J197" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K197" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt (a validar: pode estar sob outra fonte)</t>
+        </is>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M197" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente. Validar antes: a conta pode já estar coberta pela fonte idF7 ou WHAa</t>
+        </is>
+      </c>
+      <c r="N197" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O197" s="7" t="inlineStr"/>
+      <c r="P197" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q197" s="7" t="inlineStr">
+        <is>
+          <t>Ana Júlia</t>
+        </is>
+      </c>
+      <c r="R197" s="7" t="inlineStr"/>
+      <c r="S197" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T197" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U197" s="7" t="inlineStr">
+        <is>
+          <t>cliente sem fonte ligada a ele; aguardar validação de cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>SANTO REMÉDIO</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>Plano ADVANCED</t>
+        </is>
+      </c>
+      <c r="H198" s="9" t="n"/>
+      <c r="I198" s="7" t="inlineStr"/>
+      <c r="J198" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K198" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M198" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N198" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O198" s="7" t="inlineStr"/>
+      <c r="P198" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q198" s="7" t="inlineStr">
+        <is>
+          <t>Silvia Calderaro</t>
+        </is>
+      </c>
+      <c r="R198" s="7" t="inlineStr"/>
+      <c r="S198" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T198" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U198" s="7" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>SHIZEN</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H199" s="9" t="n"/>
+      <c r="I199" s="7" t="inlineStr"/>
+      <c r="J199" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K199" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M199" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N199" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O199" s="7" t="inlineStr"/>
+      <c r="P199" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q199" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R199" s="7" t="inlineStr"/>
+      <c r="S199" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T199" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U199" s="7" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>TARGO CONSULTORIA</t>
+        </is>
+      </c>
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H200" s="9" t="n"/>
+      <c r="I200" s="7" t="inlineStr"/>
+      <c r="J200" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K200" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M200" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N200" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O200" s="7" t="inlineStr"/>
+      <c r="P200" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q200" s="7" t="inlineStr"/>
+      <c r="R200" s="7" t="inlineStr"/>
+      <c r="S200" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T200" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U200" s="7" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>UNIPAR</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>(sem fonte)</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H201" s="9" t="n"/>
+      <c r="I201" s="7" t="inlineStr"/>
+      <c r="J201" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K201" s="7" t="inlineStr">
+        <is>
+          <t>Pendente — sem fonte RD Station na Nekt</t>
+        </is>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M201" s="7" t="inlineStr">
+        <is>
+          <t>Criar fonte RD Station e autorizar OAuth com usuário administrador da conta RD do cliente</t>
+        </is>
+      </c>
+      <c r="N201" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="O201" s="7" t="inlineStr"/>
+      <c r="P201" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q201" s="7" t="inlineStr">
+        <is>
+          <t>Silvia Calderaro</t>
+        </is>
+      </c>
+      <c r="R201" s="7" t="inlineStr"/>
+      <c r="S201" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="T201" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U201" s="7" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>CDL</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - CDL</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>Plano LIGHT</t>
+        </is>
+      </c>
+      <c r="H202" s="9" t="n"/>
+      <c r="I202" s="7" t="inlineStr"/>
+      <c r="J202" s="11" t="inlineStr">
+        <is>
+          <t>Bloqueada</t>
+        </is>
+      </c>
+      <c r="K202" s="7" t="inlineStr">
+        <is>
+          <t>Bloqueada — fonte inativa; 403 em /platform/campaigns (plano ou permissão do RD)</t>
+        </is>
+      </c>
+      <c r="L202" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-YLIU</t>
+        </is>
+      </c>
+      <c r="M202" s="7" t="inlineStr">
+        <is>
+          <t>Fonte desativada desde 08/09 (2 execuções, as duas com 403)</t>
+        </is>
+      </c>
+      <c r="N202" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do CDL</t>
+        </is>
+      </c>
+      <c r="O202" s="7" t="inlineStr"/>
+      <c r="P202" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q202" s="7" t="inlineStr">
+        <is>
+          <t>Betina Gava</t>
+        </is>
+      </c>
+      <c r="R202" s="7" t="inlineStr"/>
+      <c r="S202" s="7" t="inlineStr">
+        <is>
+          <t>Conferir plano/permissão da conta RD do CDL e reautorizar</t>
+        </is>
+      </c>
+      <c r="T202" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U202" s="7" t="inlineStr">
+        <is>
+          <t>sem tabela materializada</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>(RD_station_marketing)</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>RD_station_marketing</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>Fonte Nekt; cliente fora da planilha Inbound</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H203" s="9" t="n"/>
+      <c r="I203" s="7" t="inlineStr"/>
+      <c r="J203" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K203" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-oYKw</t>
+        </is>
+      </c>
+      <c r="M203" s="7" t="inlineStr">
+        <is>
+          <t>Validar se segue no escopo ativo</t>
+        </is>
+      </c>
+      <c r="N203" s="7" t="inlineStr">
+        <is>
+          <t>AM do cliente / Jussara</t>
+        </is>
+      </c>
+      <c r="O203" s="7" t="inlineStr"/>
+      <c r="P203" s="7" t="inlineStr"/>
+      <c r="Q203" s="7" t="inlineStr"/>
+      <c r="R203" s="7" t="inlineStr"/>
+      <c r="S203" s="7" t="inlineStr">
+        <is>
+          <t>Manter; confirmar escopo com o AM</t>
+        </is>
+      </c>
+      <c r="T203" s="7" t="inlineStr"/>
+      <c r="U203" s="7" t="inlineStr">
+        <is>
+          <t>167 contatos · 425 conversões · grão completo (cadastro com detalhe) · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>AC DISPLAY</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - AC DISPLAY</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H204" s="9" t="n"/>
+      <c r="I204" s="7" t="inlineStr"/>
+      <c r="J204" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K204" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L204" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-5RPi</t>
+        </is>
+      </c>
+      <c r="M204" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N204" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O204" s="7" t="inlineStr"/>
+      <c r="P204" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q204" s="7" t="inlineStr"/>
+      <c r="R204" s="7" t="inlineStr"/>
+      <c r="S204" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T204" s="7" t="inlineStr"/>
+      <c r="U204" s="7" t="inlineStr">
+        <is>
+          <t>208 contatos · 233 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>ACESSO SAÚDE MANAUS</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - ACESSO SAÚDE MANAUS</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H205" s="9" t="n"/>
+      <c r="I205" s="7" t="inlineStr"/>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K205" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-Awhd</t>
+        </is>
+      </c>
+      <c r="M205" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N205" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O205" s="7" t="inlineStr"/>
+      <c r="P205" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q205" s="7" t="inlineStr">
+        <is>
+          <t>Ana Júlia</t>
+        </is>
+      </c>
+      <c r="R205" s="7" t="inlineStr"/>
+      <c r="S205" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T205" s="7" t="inlineStr"/>
+      <c r="U205" s="7" t="inlineStr">
+        <is>
+          <t>731 contatos · 1.126 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>AMAZON OPEN MALL</t>
+        </is>
+      </c>
+      <c r="C206" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - AMAZON OPEN MALL</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Plano BASIC</t>
+        </is>
+      </c>
+      <c r="H206" s="9" t="n"/>
+      <c r="I206" s="7" t="inlineStr"/>
+      <c r="J206" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K206" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L206" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-AqsD</t>
+        </is>
+      </c>
+      <c r="M206" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N206" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O206" s="7" t="inlineStr"/>
+      <c r="P206" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q206" s="7" t="inlineStr">
+        <is>
+          <t>Betina Gava</t>
+        </is>
+      </c>
+      <c r="R206" s="7" t="inlineStr"/>
+      <c r="S206" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T206" s="7" t="inlineStr"/>
+      <c r="U206" s="7" t="inlineStr">
+        <is>
+          <t>129 contatos · 197 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>AMAZONCOPY</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - AMAZONCOPY</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H207" s="9" t="n"/>
+      <c r="I207" s="7" t="inlineStr"/>
+      <c r="J207" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K207" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-9mbj</t>
+        </is>
+      </c>
+      <c r="M207" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N207" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O207" s="7" t="inlineStr"/>
+      <c r="P207" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q207" s="7" t="inlineStr">
+        <is>
+          <t>Yanka Gabriela</t>
+        </is>
+      </c>
+      <c r="R207" s="7" t="inlineStr"/>
+      <c r="S207" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T207" s="7" t="inlineStr"/>
+      <c r="U207" s="7" t="inlineStr">
+        <is>
+          <t>480 contatos · 518 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>AMZ GERADORES</t>
+        </is>
+      </c>
+      <c r="C208" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - AMZ GERADORES</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H208" s="9" t="n"/>
+      <c r="I208" s="7" t="inlineStr"/>
+      <c r="J208" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K208" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L208" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-CSrx</t>
+        </is>
+      </c>
+      <c r="M208" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N208" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O208" s="7" t="inlineStr"/>
+      <c r="P208" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q208" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R208" s="7" t="inlineStr"/>
+      <c r="S208" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T208" s="7" t="inlineStr"/>
+      <c r="U208" s="7" t="inlineStr">
+        <is>
+          <t>170 contatos · 432 conversões · grão completo (cadastro com detalhe) · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>AMZ IMPORTS</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - AMZ IMPORTS</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H209" s="9" t="n"/>
+      <c r="I209" s="7" t="inlineStr"/>
+      <c r="J209" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K209" s="7" t="inlineStr">
+        <is>
+          <t>Conectada — executa com sucesso, mas nenhuma tabela materializada (não entra na Trusted)</t>
+        </is>
+      </c>
+      <c r="L209" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-socq</t>
+        </is>
+      </c>
+      <c r="M209" s="7" t="inlineStr">
+        <is>
+          <t>Fonte roda todo dia 12:40 e não entrega dado; causa não verificada</t>
+        </is>
+      </c>
+      <c r="N209" s="7" t="inlineStr">
+        <is>
+          <t>Jussara (diagnóstico na Nekt) + Analista Inbound (Joyce)</t>
+        </is>
+      </c>
+      <c r="O209" s="7" t="inlineStr"/>
+      <c r="P209" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q209" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R209" s="7" t="inlineStr"/>
+      <c r="S209" s="7" t="inlineStr">
+        <is>
+          <t>Conferir se a conta RD do cliente tem contatos/conversões e a permissão da API</t>
+        </is>
+      </c>
+      <c r="T209" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="U209" s="7" t="inlineStr">
+        <is>
+          <t>0 tabelas na camada; Fonte roda sem entregar dado</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>BA ELÉTRICA</t>
+        </is>
+      </c>
+      <c r="C210" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - BA ELÉTRICA</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H210" s="9" t="n"/>
+      <c r="I210" s="7" t="inlineStr"/>
+      <c r="J210" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K210" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L210" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-MzyH</t>
+        </is>
+      </c>
+      <c r="M210" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N210" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O210" s="7" t="inlineStr"/>
+      <c r="P210" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q210" s="7" t="inlineStr">
+        <is>
+          <t>Fabiane Carvalho</t>
+        </is>
+      </c>
+      <c r="R210" s="7" t="inlineStr"/>
+      <c r="S210" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T210" s="7" t="inlineStr"/>
+      <c r="U210" s="7" t="inlineStr">
+        <is>
+          <t>125 contatos · 247 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>BEST CAR</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - BEST CAR</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H211" s="9" t="n"/>
+      <c r="I211" s="7" t="inlineStr"/>
+      <c r="J211" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K211" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L211" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-pG4G</t>
+        </is>
+      </c>
+      <c r="M211" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N211" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O211" s="7" t="inlineStr"/>
+      <c r="P211" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q211" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R211" s="7" t="inlineStr"/>
+      <c r="S211" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T211" s="7" t="inlineStr"/>
+      <c r="U211" s="7" t="inlineStr">
+        <is>
+          <t>5.824 contatos · 5.837 conversões · grão completo (cadastro com detalhe) · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>BIGAZINE MANAUS</t>
+        </is>
+      </c>
+      <c r="C212" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - BIGAZINE MANAUS</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H212" s="9" t="n"/>
+      <c r="I212" s="7" t="inlineStr"/>
+      <c r="J212" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K212" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L212" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-urW3</t>
+        </is>
+      </c>
+      <c r="M212" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N212" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O212" s="7" t="inlineStr"/>
+      <c r="P212" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q212" s="7" t="inlineStr">
+        <is>
+          <t>Fabiane Carvalho</t>
+        </is>
+      </c>
+      <c r="R212" s="7" t="inlineStr"/>
+      <c r="S212" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T212" s="7" t="inlineStr"/>
+      <c r="U212" s="7" t="inlineStr">
+        <is>
+          <t>3.558 contatos · 2.963 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>BRAGA ACESSÓRIOS</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - BRAGA ACESSÓRIOS</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H213" s="9" t="n"/>
+      <c r="I213" s="7" t="inlineStr"/>
+      <c r="J213" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K213" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L213" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-8Fqy</t>
+        </is>
+      </c>
+      <c r="M213" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N213" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O213" s="7" t="inlineStr"/>
+      <c r="P213" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q213" s="7" t="inlineStr">
+        <is>
+          <t>Ana Júlia</t>
+        </is>
+      </c>
+      <c r="R213" s="7" t="inlineStr"/>
+      <c r="S213" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T213" s="7" t="inlineStr"/>
+      <c r="U213" s="7" t="inlineStr">
+        <is>
+          <t>186 contatos · 201 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>BRAGA MOTORS</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - BRAGA MOTORS</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H214" s="9" t="n"/>
+      <c r="I214" s="7" t="inlineStr"/>
+      <c r="J214" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K214" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L214" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-idF7</t>
+        </is>
+      </c>
+      <c r="M214" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N214" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O214" s="7" t="inlineStr"/>
+      <c r="P214" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q214" s="7" t="inlineStr">
+        <is>
+          <t>Silvia Calderaro</t>
+        </is>
+      </c>
+      <c r="R214" s="7" t="inlineStr"/>
+      <c r="S214" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T214" s="7" t="inlineStr"/>
+      <c r="U214" s="7" t="inlineStr">
+        <is>
+          <t>255 contatos · 399 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>BRAGA VEÍCULOS (a validar)</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - BRAGA VEICULOS</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>Fonte Nekt; a descrição não coincide com cliente da planilha Inbound (3 unidades Braga Veículos)</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H215" s="9" t="n"/>
+      <c r="I215" s="7" t="inlineStr"/>
+      <c r="J215" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K215" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L215" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-WHAa</t>
+        </is>
+      </c>
+      <c r="M215" s="7" t="inlineStr">
+        <is>
+          <t>Validar quais unidades Braga Veículos (venda direta, pós-venda, varejo) esta conta RD cobre</t>
+        </is>
+      </c>
+      <c r="N215" s="7" t="inlineStr">
+        <is>
+          <t>AM do cliente / Jussara</t>
+        </is>
+      </c>
+      <c r="O215" s="7" t="inlineStr"/>
+      <c r="P215" s="7" t="inlineStr"/>
+      <c r="Q215" s="7" t="inlineStr">
+        <is>
+          <t>Igor Luís</t>
+        </is>
+      </c>
+      <c r="R215" s="7" t="inlineStr"/>
+      <c r="S215" s="7" t="inlineStr">
+        <is>
+          <t>Manter; confirmar escopo com o AM</t>
+        </is>
+      </c>
+      <c r="T215" s="7" t="inlineStr"/>
+      <c r="U215" s="7" t="inlineStr">
+        <is>
+          <t>311 contatos · 482 conversões · grão completo (cadastro com detalhe) · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>COMAC</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - COMAC</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H216" s="9" t="n"/>
+      <c r="I216" s="7" t="inlineStr"/>
+      <c r="J216" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K216" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L216" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-uOAA</t>
+        </is>
+      </c>
+      <c r="M216" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N216" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O216" s="7" t="inlineStr"/>
+      <c r="P216" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q216" s="7" t="inlineStr">
+        <is>
+          <t>Yanka Gabriela</t>
+        </is>
+      </c>
+      <c r="R216" s="7" t="inlineStr"/>
+      <c r="S216" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T216" s="7" t="inlineStr"/>
+      <c r="U216" s="7" t="inlineStr">
+        <is>
+          <t>187 contatos · 70 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA COLMEIA</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - CONSTRUTORA COLMEIA</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H217" s="9" t="n"/>
+      <c r="I217" s="7" t="inlineStr"/>
+      <c r="J217" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K217" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L217" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-VYbu</t>
+        </is>
+      </c>
+      <c r="M217" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N217" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O217" s="7" t="inlineStr"/>
+      <c r="P217" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q217" s="7" t="inlineStr">
+        <is>
+          <t>Igor Luís</t>
+        </is>
+      </c>
+      <c r="R217" s="7" t="inlineStr"/>
+      <c r="S217" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T217" s="7" t="inlineStr"/>
+      <c r="U217" s="7" t="inlineStr">
+        <is>
+          <t>3.271 contatos · 14.182 conversões · grão completo (cadastro com detalhe) · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>DMELLO</t>
+        </is>
+      </c>
+      <c r="C218" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - DMELLO</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>Fonte Nekt; cliente fora da planilha Inbound</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H218" s="9" t="n"/>
+      <c r="I218" s="7" t="inlineStr"/>
+      <c r="J218" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K218" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L218" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-3k4Z</t>
+        </is>
+      </c>
+      <c r="M218" s="7" t="inlineStr">
+        <is>
+          <t>Validar se segue no escopo ativo</t>
+        </is>
+      </c>
+      <c r="N218" s="7" t="inlineStr">
+        <is>
+          <t>AM do cliente / Jussara</t>
+        </is>
+      </c>
+      <c r="O218" s="7" t="inlineStr"/>
+      <c r="P218" s="7" t="inlineStr"/>
+      <c r="Q218" s="7" t="inlineStr"/>
+      <c r="R218" s="7" t="inlineStr"/>
+      <c r="S218" s="7" t="inlineStr">
+        <is>
+          <t>Manter; confirmar escopo com o AM</t>
+        </is>
+      </c>
+      <c r="T218" s="7" t="inlineStr"/>
+      <c r="U218" s="7" t="inlineStr">
+        <is>
+          <t>287 contatos · 380 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>DON WATCHES</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - DON WATCHES</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>Fonte Nekt; cliente fora da planilha Inbound</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H219" s="9" t="n"/>
+      <c r="I219" s="7" t="inlineStr"/>
+      <c r="J219" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K219" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L219" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-dvZx</t>
+        </is>
+      </c>
+      <c r="M219" s="7" t="inlineStr">
+        <is>
+          <t>Validar se segue no escopo ativo</t>
+        </is>
+      </c>
+      <c r="N219" s="7" t="inlineStr">
+        <is>
+          <t>AM do cliente / Jussara</t>
+        </is>
+      </c>
+      <c r="O219" s="7" t="inlineStr"/>
+      <c r="P219" s="7" t="inlineStr"/>
+      <c r="Q219" s="7" t="inlineStr"/>
+      <c r="R219" s="7" t="inlineStr"/>
+      <c r="S219" s="7" t="inlineStr">
+        <is>
+          <t>Manter; confirmar escopo com o AM</t>
+        </is>
+      </c>
+      <c r="T219" s="7" t="inlineStr"/>
+      <c r="U219" s="7" t="inlineStr">
+        <is>
+          <t>147 contatos · 301 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>DR. JOSÉ CABRAL JR.</t>
+        </is>
+      </c>
+      <c r="C220" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - DR. JOSÉ CABRAL JR.</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H220" s="9" t="n"/>
+      <c r="I220" s="7" t="inlineStr"/>
+      <c r="J220" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K220" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L220" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-L2Sl</t>
+        </is>
+      </c>
+      <c r="M220" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N220" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O220" s="7" t="inlineStr"/>
+      <c r="P220" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q220" s="7" t="inlineStr"/>
+      <c r="R220" s="7" t="inlineStr"/>
+      <c r="S220" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T220" s="7" t="inlineStr"/>
+      <c r="U220" s="7" t="inlineStr">
+        <is>
+          <t>458 contatos · 582 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>HOPE BAY</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - HOPE BAY</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>Fonte Nekt; cliente fora da planilha Inbound</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H221" s="9" t="n"/>
+      <c r="I221" s="7" t="inlineStr"/>
+      <c r="J221" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K221" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L221" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-HoWi</t>
+        </is>
+      </c>
+      <c r="M221" s="7" t="inlineStr">
+        <is>
+          <t>Validar se segue no escopo ativo</t>
+        </is>
+      </c>
+      <c r="N221" s="7" t="inlineStr">
+        <is>
+          <t>AM do cliente / Jussara</t>
+        </is>
+      </c>
+      <c r="O221" s="7" t="inlineStr"/>
+      <c r="P221" s="7" t="inlineStr"/>
+      <c r="Q221" s="7" t="inlineStr"/>
+      <c r="R221" s="7" t="inlineStr"/>
+      <c r="S221" s="7" t="inlineStr">
+        <is>
+          <t>Manter; confirmar escopo com o AM</t>
+        </is>
+      </c>
+      <c r="T221" s="7" t="inlineStr"/>
+      <c r="U221" s="7" t="inlineStr">
+        <is>
+          <t>2.010 contatos · 2.012 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>HOSPITAL SANTA JÚLIA</t>
+        </is>
+      </c>
+      <c r="C222" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - HOSPITAL SANTA JÚLIA</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H222" s="9" t="n"/>
+      <c r="I222" s="7" t="inlineStr"/>
+      <c r="J222" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K222" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L222" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-STKa</t>
+        </is>
+      </c>
+      <c r="M222" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N222" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O222" s="7" t="inlineStr"/>
+      <c r="P222" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q222" s="7" t="inlineStr">
+        <is>
+          <t>Fabiane Carvalho</t>
+        </is>
+      </c>
+      <c r="R222" s="7" t="inlineStr"/>
+      <c r="S222" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T222" s="7" t="inlineStr"/>
+      <c r="U222" s="7" t="inlineStr">
+        <is>
+          <t>885 contatos · 1.169 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>INFORCELL</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - INFORCELL</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H223" s="9" t="n"/>
+      <c r="I223" s="7" t="inlineStr"/>
+      <c r="J223" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K223" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L223" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-sLX1</t>
+        </is>
+      </c>
+      <c r="M223" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N223" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O223" s="7" t="inlineStr"/>
+      <c r="P223" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q223" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R223" s="7" t="inlineStr"/>
+      <c r="S223" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T223" s="7" t="inlineStr"/>
+      <c r="U223" s="7" t="inlineStr">
+        <is>
+          <t>126 contatos · 130 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>KL RENT A CAR</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - KL RENT A CAR</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H224" s="9" t="n"/>
+      <c r="I224" s="7" t="inlineStr"/>
+      <c r="J224" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K224" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L224" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-Ozim</t>
+        </is>
+      </c>
+      <c r="M224" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N224" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O224" s="7" t="inlineStr"/>
+      <c r="P224" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q224" s="7" t="inlineStr">
+        <is>
+          <t>Jeremias Oliveira</t>
+        </is>
+      </c>
+      <c r="R224" s="7" t="inlineStr"/>
+      <c r="S224" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T224" s="7" t="inlineStr"/>
+      <c r="U224" s="7" t="inlineStr">
+        <is>
+          <t>83.718 contatos · 83.224 conversões · grão completo (cadastro com detalhe) · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>MARAVILHA MOTOS</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - MARAVILHA MOTOS</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H225" s="9" t="n"/>
+      <c r="I225" s="7" t="inlineStr"/>
+      <c r="J225" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K225" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L225" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-CWtQ</t>
+        </is>
+      </c>
+      <c r="M225" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N225" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O225" s="7" t="inlineStr"/>
+      <c r="P225" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q225" s="7" t="inlineStr"/>
+      <c r="R225" s="7" t="inlineStr"/>
+      <c r="S225" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T225" s="7" t="inlineStr"/>
+      <c r="U225" s="7" t="inlineStr">
+        <is>
+          <t>129 contatos · 270 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>MILLENNIUM SHOPPING</t>
+        </is>
+      </c>
+      <c r="C226" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - MILLENNIUM SHOPPING</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>Plano BASIC</t>
+        </is>
+      </c>
+      <c r="H226" s="9" t="n"/>
+      <c r="I226" s="7" t="inlineStr"/>
+      <c r="J226" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K226" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L226" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-4b7D</t>
+        </is>
+      </c>
+      <c r="M226" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N226" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O226" s="7" t="inlineStr"/>
+      <c r="P226" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q226" s="7" t="inlineStr">
+        <is>
+          <t>Betina Gava</t>
+        </is>
+      </c>
+      <c r="R226" s="7" t="inlineStr"/>
+      <c r="S226" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T226" s="7" t="inlineStr"/>
+      <c r="U226" s="7" t="inlineStr">
+        <is>
+          <t>191 contatos · 204 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>MOVE</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - MOVE</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="n"/>
+      <c r="I227" s="7" t="inlineStr"/>
+      <c r="J227" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K227" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L227" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-sPoP</t>
+        </is>
+      </c>
+      <c r="M227" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N227" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O227" s="7" t="inlineStr"/>
+      <c r="P227" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q227" s="7" t="inlineStr"/>
+      <c r="R227" s="7" t="inlineStr"/>
+      <c r="S227" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T227" s="7" t="inlineStr"/>
+      <c r="U227" s="7" t="inlineStr">
+        <is>
+          <t>1.487 contatos · 1.351 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>PMZ</t>
+        </is>
+      </c>
+      <c r="C228" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - PMZ</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H228" s="9" t="n"/>
+      <c r="I228" s="7" t="inlineStr"/>
+      <c r="J228" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K228" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L228" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-bdVN</t>
+        </is>
+      </c>
+      <c r="M228" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N228" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O228" s="7" t="inlineStr"/>
+      <c r="P228" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q228" s="7" t="inlineStr"/>
+      <c r="R228" s="7" t="inlineStr"/>
+      <c r="S228" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T228" s="7" t="inlineStr"/>
+      <c r="U228" s="7" t="inlineStr">
+        <is>
+          <t>341 contatos · 570 conversões · grão completo (cadastro com detalhe) · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>PNEU FORTE</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - PNEU FORTE</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H229" s="9" t="n"/>
+      <c r="I229" s="7" t="inlineStr"/>
+      <c r="J229" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K229" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L229" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-7K57</t>
+        </is>
+      </c>
+      <c r="M229" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N229" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O229" s="7" t="inlineStr"/>
+      <c r="P229" s="7" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="Q229" s="7" t="inlineStr">
+        <is>
+          <t>Yanka Gabriela</t>
+        </is>
+      </c>
+      <c r="R229" s="7" t="inlineStr"/>
+      <c r="S229" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T229" s="7" t="inlineStr"/>
+      <c r="U229" s="7" t="inlineStr">
+        <is>
+          <t>231 contatos · 260 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>REI DAS MANGUEIRAS</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - REI DAS MANGUEIRAS</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>Plano LIGHT</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="n"/>
+      <c r="I230" s="7" t="inlineStr"/>
+      <c r="J230" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K230" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L230" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-h3u2</t>
+        </is>
+      </c>
+      <c r="M230" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N230" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O230" s="7" t="inlineStr"/>
+      <c r="P230" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q230" s="7" t="inlineStr">
+        <is>
+          <t>Fernanda Bonates</t>
+        </is>
+      </c>
+      <c r="R230" s="7" t="inlineStr"/>
+      <c r="S230" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T230" s="7" t="inlineStr"/>
+      <c r="U230" s="7" t="inlineStr">
+        <is>
+          <t>296 contatos · 326 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>STEEL PORT</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - STEEL PORT</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>Plano BASIC</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="n"/>
+      <c r="I231" s="7" t="inlineStr"/>
+      <c r="J231" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K231" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L231" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-HVbj</t>
+        </is>
+      </c>
+      <c r="M231" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N231" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O231" s="7" t="inlineStr"/>
+      <c r="P231" s="7" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="Q231" s="7" t="inlineStr">
+        <is>
+          <t>Fernanda Bonates</t>
+        </is>
+      </c>
+      <c r="R231" s="7" t="inlineStr"/>
+      <c r="S231" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T231" s="7" t="inlineStr"/>
+      <c r="U231" s="7" t="inlineStr">
+        <is>
+          <t>95 contatos · 123 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>VANGUARDA</t>
+        </is>
+      </c>
+      <c r="C232" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>RD_clientes_vanguarda</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H232" s="9" t="n"/>
+      <c r="I232" s="7" t="inlineStr"/>
+      <c r="J232" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K232" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L232" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-pDLk</t>
+        </is>
+      </c>
+      <c r="M232" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N232" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O232" s="7" t="inlineStr"/>
+      <c r="P232" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q232" s="7" t="inlineStr"/>
+      <c r="R232" s="7" t="inlineStr"/>
+      <c r="S232" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T232" s="7" t="inlineStr"/>
+      <c r="U232" s="7" t="inlineStr">
+        <is>
+          <t>4.789 contatos · 6.149 conversões · grão completo (cadastro com detalhe) · carga 13/10; as fontes 1eaJ e bjQx ("BD - RD STATION - VANGUARDA") são cópias desta conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>VBOT</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - VBOT</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>Planilha Inbound (plano RD)</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>Plano PRO</t>
+        </is>
+      </c>
+      <c r="H233" s="9" t="n"/>
+      <c r="I233" s="7" t="inlineStr"/>
+      <c r="J233" s="12" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+      <c r="K233" s="7" t="inlineStr">
+        <is>
+          <t>Conectada e extraindo</t>
+        </is>
+      </c>
+      <c r="L233" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-iJK3</t>
+        </is>
+      </c>
+      <c r="M233" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N233" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O233" s="7" t="inlineStr"/>
+      <c r="P233" s="7" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="Q233" s="7" t="inlineStr">
+        <is>
+          <t>Betina Gava</t>
+        </is>
+      </c>
+      <c r="R233" s="7" t="inlineStr"/>
+      <c r="S233" s="7" t="inlineStr">
+        <is>
+          <t>Manter; acompanhar carga diária</t>
+        </is>
+      </c>
+      <c r="T233" s="7" t="inlineStr"/>
+      <c r="U233" s="7" t="inlineStr">
+        <is>
+          <t>279 contatos · 454 conversões · grão mínimo: só id. e-mail e última conversão · carga 13/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>VANGUARDA (duplicata)</t>
+        </is>
+      </c>
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - VANGUARDA</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>Fonte Nekt; duplicata da RD_clientes_vanguarda (pDLk)</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="n"/>
+      <c r="I234" s="7" t="inlineStr"/>
+      <c r="J234" s="13" t="inlineStr">
+        <is>
+          <t>Não precisa manter (a validar)</t>
+        </is>
+      </c>
+      <c r="K234" s="7" t="inlineStr">
+        <is>
+          <t>Possivelmente dispensável — duplicata da pDLk (mesma conta RD extraída 3×; fora da Trusted por decisão de 01/09, reconferida em 28/09)</t>
+        </is>
+      </c>
+      <c r="L234" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-1eaJ</t>
+        </is>
+      </c>
+      <c r="M234" s="7" t="inlineStr">
+        <is>
+          <t>Consome execução diária sem acrescentar dado</t>
+        </is>
+      </c>
+      <c r="N234" s="7" t="inlineStr">
+        <is>
+          <t>Jussara (decisão; R-002 impede alterar sem pedido)</t>
+        </is>
+      </c>
+      <c r="O234" s="7" t="inlineStr"/>
+      <c r="P234" s="7" t="inlineStr"/>
+      <c r="Q234" s="7" t="inlineStr"/>
+      <c r="R234" s="7" t="inlineStr"/>
+      <c r="S234" s="7" t="inlineStr">
+        <is>
+          <t>Sugerido encerrar a fonte; não alterada</t>
+        </is>
+      </c>
+      <c r="T234" s="7" t="inlineStr"/>
+      <c r="U234" s="7" t="inlineStr">
+        <is>
+          <t>só 1 contato fora da pDLk (e-mail de teste)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>VANGUARDA (duplicata)</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D235" s="7" t="inlineStr">
+        <is>
+          <t>BD - RD STATION - VANGUARDA</t>
+        </is>
+      </c>
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>Fonte Nekt; duplicata da RD_clientes_vanguarda (pDLk)</t>
+        </is>
+      </c>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="n"/>
+      <c r="I235" s="7" t="inlineStr"/>
+      <c r="J235" s="13" t="inlineStr">
+        <is>
+          <t>Não precisa manter (a validar)</t>
+        </is>
+      </c>
+      <c r="K235" s="7" t="inlineStr">
+        <is>
+          <t>Possivelmente dispensável — duplicata da pDLk (mesma conta RD extraída 3×; fora da Trusted por decisão de 01/09, reconferida em 28/09)</t>
+        </is>
+      </c>
+      <c r="L235" s="7" t="inlineStr">
+        <is>
+          <t>rd-station-bjQx</t>
+        </is>
+      </c>
+      <c r="M235" s="7" t="inlineStr">
+        <is>
+          <t>Consome execução diária sem acrescentar dado</t>
+        </is>
+      </c>
+      <c r="N235" s="7" t="inlineStr">
+        <is>
+          <t>Jussara (decisão; R-002 impede alterar sem pedido)</t>
+        </is>
+      </c>
+      <c r="O235" s="7" t="inlineStr"/>
+      <c r="P235" s="7" t="inlineStr"/>
+      <c r="Q235" s="7" t="inlineStr"/>
+      <c r="R235" s="7" t="inlineStr"/>
+      <c r="S235" s="7" t="inlineStr">
+        <is>
+          <t>Sugerido encerrar a fonte; não alterada</t>
+        </is>
+      </c>
+      <c r="T235" s="7" t="inlineStr"/>
+      <c r="U235" s="7" t="inlineStr">
+        <is>
+          <t>só 1 contato fora da pDLk (e-mail de teste)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>Spotify Ads</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>PÁTIO GOURMET (LOJAS)</t>
+        </is>
+      </c>
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>conta não informada nos documentos</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>Planilha de divisão por squad</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H236" s="9" t="n"/>
+      <c r="I236" s="7" t="inlineStr"/>
+      <c r="J236" s="14" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+      <c r="K236" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão — não há conector Nekt para esta plataforma</t>
+        </is>
+      </c>
+      <c r="L236" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M236" s="7" t="inlineStr">
+        <is>
+          <t>ID da conta não consta em nenhum documento</t>
+        </is>
+      </c>
+      <c r="N236" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="O236" s="7" t="inlineStr"/>
+      <c r="P236" s="7" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="Q236" s="7" t="inlineStr"/>
+      <c r="R236" s="7" t="inlineStr"/>
+      <c r="S236" s="7" t="inlineStr">
+        <is>
           <t>Levantar ID da conta e decidir se entra no escopo</t>
         </is>
       </c>
-      <c r="T183" s="7" t="inlineStr">
+      <c r="T236" s="7" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="U183" s="7" t="inlineStr"/>
+      <c r="U236" s="7" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>TikTok Ads</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>BA ELÉTRICA</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D237" s="7" t="inlineStr">
+        <is>
+          <t>conta não informada nos documentos</t>
+        </is>
+      </c>
+      <c r="E237" s="7" t="inlineStr">
+        <is>
+          <t>Planilha de divisão por squad</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="n"/>
+      <c r="I237" s="7" t="inlineStr"/>
+      <c r="J237" s="14" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+      <c r="K237" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+        </is>
+      </c>
+      <c r="L237" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M237" s="7" t="inlineStr">
+        <is>
+          <t>ID da conta não consta em nenhum documento</t>
+        </is>
+      </c>
+      <c r="N237" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="O237" s="7" t="inlineStr">
+        <is>
+          <t>Gabrielly</t>
+        </is>
+      </c>
+      <c r="P237" s="7" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="Q237" s="7" t="inlineStr">
+        <is>
+          <t>Fabiane Carvalho</t>
+        </is>
+      </c>
+      <c r="R237" s="7" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="S237" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="T237" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U237" s="7" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>TikTok Ads</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>PÁTIO GOURMET (LOJAS)</t>
+        </is>
+      </c>
+      <c r="C238" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>conta não informada nos documentos</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>Planilha de divisão por squad</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H238" s="9" t="n"/>
+      <c r="I238" s="7" t="inlineStr"/>
+      <c r="J238" s="14" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+      <c r="K238" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+        </is>
+      </c>
+      <c r="L238" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M238" s="7" t="inlineStr">
+        <is>
+          <t>ID da conta não consta em nenhum documento</t>
+        </is>
+      </c>
+      <c r="N238" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="O238" s="7" t="inlineStr"/>
+      <c r="P238" s="7" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="Q238" s="7" t="inlineStr"/>
+      <c r="R238" s="7" t="inlineStr"/>
+      <c r="S238" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="T238" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U238" s="7" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>TikTok Ads</t>
+        </is>
+      </c>
+      <c r="B239" s="7" t="inlineStr">
+        <is>
+          <t>SANTO REMÉDIO</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>conta não informada nos documentos</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>Planilha de divisão por squad</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H239" s="9" t="n"/>
+      <c r="I239" s="7" t="inlineStr"/>
+      <c r="J239" s="14" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+      <c r="K239" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+        </is>
+      </c>
+      <c r="L239" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M239" s="7" t="inlineStr">
+        <is>
+          <t>ID da conta não consta em nenhum documento</t>
+        </is>
+      </c>
+      <c r="N239" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="O239" s="7" t="inlineStr">
+        <is>
+          <t>Wilkefor</t>
+        </is>
+      </c>
+      <c r="P239" s="7" t="inlineStr">
+        <is>
+          <t>Wilkefor</t>
+        </is>
+      </c>
+      <c r="Q239" s="7" t="inlineStr">
+        <is>
+          <t>Silvia Calderaro</t>
+        </is>
+      </c>
+      <c r="R239" s="7" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="S239" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="T239" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U239" s="7" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
+        <is>
+          <t>TikTok Ads</t>
+        </is>
+      </c>
+      <c r="B240" s="7" t="inlineStr">
+        <is>
+          <t>TUBOAÇOS</t>
+        </is>
+      </c>
+      <c r="C240" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>conta não informada nos documentos</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>Planilha de divisão por squad</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H240" s="9" t="n"/>
+      <c r="I240" s="7" t="inlineStr"/>
+      <c r="J240" s="14" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+      <c r="K240" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão — conector tiktok-ads existe na Nekt, nenhuma fonte criada</t>
+        </is>
+      </c>
+      <c r="L240" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M240" s="7" t="inlineStr">
+        <is>
+          <t>ID da conta não consta em nenhum documento</t>
+        </is>
+      </c>
+      <c r="N240" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="O240" s="7" t="inlineStr"/>
+      <c r="P240" s="7" t="inlineStr">
+        <is>
+          <t>Bruno</t>
+        </is>
+      </c>
+      <c r="Q240" s="7" t="inlineStr"/>
+      <c r="R240" s="7" t="inlineStr"/>
+      <c r="S240" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="T240" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U240" s="7" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="7" t="inlineStr">
+        <is>
+          <t>Twitter/X Ads</t>
+        </is>
+      </c>
+      <c r="B241" s="7" t="inlineStr">
+        <is>
+          <t>PÁTIO GOURMET (LOJAS)</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D241" s="7" t="inlineStr">
+        <is>
+          <t>conta não informada nos documentos</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>Planilha de divisão por squad</t>
+        </is>
+      </c>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G241" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H241" s="9" t="n"/>
+      <c r="I241" s="7" t="inlineStr"/>
+      <c r="J241" s="14" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+      <c r="K241" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão — não há conector Nekt para esta plataforma</t>
+        </is>
+      </c>
+      <c r="L241" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M241" s="7" t="inlineStr">
+        <is>
+          <t>ID da conta não consta em nenhum documento</t>
+        </is>
+      </c>
+      <c r="N241" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="O241" s="7" t="inlineStr"/>
+      <c r="P241" s="7" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="Q241" s="7" t="inlineStr"/>
+      <c r="R241" s="7" t="inlineStr"/>
+      <c r="S241" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="T241" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="U241" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U183"/>
+  <autoFilter ref="A1:U241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17652,7 +22711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18124,215 +23183,460 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Administrador do MCC Google Ads 170-443-9246 (a confirmar)</t>
+          <t>Analista Inbound (Bryan) + admin da conta RD do CDL</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Reautorizar no prazo da Google (23/10)</t>
+          <t>Conferir plano/permissão da conta RD do CDL e reautorizar</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>ACESSO SAÚDE; AMAZONCOPY; AMZ GERADORES; ARENA TINTAS; BA ELÉTRICA; BIGAZINE; BRAGA ACESSÓRIOS; BRAGA MINI; BRAGA MOTORRAD | MOTO BMW; BRAGA MOTORS BMW; BRAGA PÓS VENDAS; BRAGA VAREJO; BRAGA YAMAHA; BRAGA YAMAHA CONSÓRCIOS; CAA ALUMÍNIO; CAA TINTAS; COLMEIA; CONSTRÓI INCORPORADORA; DEB TRANSPORTADORA; DOCTOR MAIS; DON WATCHES (conta 2); HOSPITAL SANTA JÚLIA; MILLENIUM; MOVE RENTAL CARS; OLÁ CASA NOVA; PMZ ESCOLA DE MECÂNICOS; PMZ GRUPO ECOMM; PMZ GRUPO LOJA; PNEU EXPRESS; PNEU FORTE DISTRIBUIDORA; REI DAS MANGUEIRAS; RODRIX; ROYAL ENFIELD; SMILE PNEUS; STEEL PORT; UNIPAR</t>
+          <t>CDL</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Conectada</t>
+          <t>Bloqueada</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Jussara + administrador do MCC</t>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Não integrar; solicitar desvínculo da conta do MCC</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>LOJA | NOVA ERA BV | PIX; LOJA | NOVA ERA PVH | PIX; NOVA ERA MAO | LOJAS; NOVA ERA | MANAUS | ECOMM; NOVA ERA | PORTO VELHO | ECOMM</t>
+          <t>HAGE ALIMENTOS; RODRIX</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Fora do escopo (Nova Era)</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>ALMEIDA E BARRETO; AMAZONCOPY; PRESTEX; TUBOAÇOS</t>
+          <t>ARENA TINTAS; BRAGA MOTOS - YAMAHA - PÓS VENDAS; BRAGA MOTOS - YAMAHA - VENDAS; CAA ALUMÍNIO; CAA TINTAS; DISTRIBUIDORA PNEU FORTE; ROYAL ENFIELD; SANTO REMÉDIO; SHIZEN; UNIPAR</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Spotify Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>PÁTIO GOURMET (LOJAS)</t>
+          <t>BAJAJ; BAP; BRAGA VEÍCULOS - VENDA DIRETA; BRAGA VEÍCULOS VAREJO; BRAGA VEÍCULOS VENDAS - PÓS VENDA; CONSTROI INCORPORADORA; DOCTOR MAIS SAÚDE; PMZ ESCOLA</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>RD Station</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Jussara (diagnóstico na Nekt) + Analista Inbound (Joyce)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo</t>
+          <t>Conferir se a conta RD do cliente tem contatos/conversões e a permissão da API</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>BA ELÉTRICA; PÁTIO GOURMET (LOJAS); SANTO REMÉDIO; TUBOAÇOS</t>
+          <t>AMZ IMPORTS</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Sem conexão</t>
+          <t>Conectada</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Administrador do MCC Google Ads 170-443-9246 (a confirmar)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Reautorizar no prazo da Google (23/10)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>ACESSO SAÚDE; AMAZONCOPY; AMZ GERADORES; ARENA TINTAS; BA ELÉTRICA; BIGAZINE; BRAGA ACESSÓRIOS; BRAGA MINI; BRAGA MOTORRAD | MOTO BMW; BRAGA MOTORS BMW; BRAGA PÓS VENDAS; BRAGA VAREJO; BRAGA YAMAHA; BRAGA YAMAHA CONSÓRCIOS; CAA ALUMÍNIO; CAA TINTAS; COLMEIA; CONSTRÓI INCORPORADORA; DEB TRANSPORTADORA; DOCTOR MAIS; DON WATCHES (conta 2); HOSPITAL SANTA JÚLIA; MILLENIUM; MOVE RENTAL CARS; OLÁ CASA NOVA; PMZ ESCOLA DE MECÂNICOS; PMZ GRUPO ECOMM; PMZ GRUPO LOJA; PNEU EXPRESS; PNEU FORTE DISTRIBUIDORA; REI DAS MANGUEIRAS; RODRIX; ROYAL ENFIELD; SMILE PNEUS; STEEL PORT; UNIPAR</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Conectada</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Jussara + administrador do MCC</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Não integrar; solicitar desvínculo da conta do MCC</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>LOJA | NOVA ERA BV | PIX; LOJA | NOVA ERA PVH | PIX; NOVA ERA MAO | LOJAS; NOVA ERA | MANAUS | ECOMM; NOVA ERA | PORTO VELHO | ECOMM</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Fora do escopo (Nova Era)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>LinkedIn Ads</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>ALMEIDA E BARRETO; AMAZONCOPY; PRESTEX; TUBOAÇOS</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>LEGACY PNEUS; LOVOL; TARGO CONSULTORIA</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>RD Station</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>CHARÃO</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Spotify Ads</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>PÁTIO GOURMET (LOJAS)</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>TikTok Ads</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Analista da conta</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Levantar ID da conta e decidir se entra no escopo</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>BA ELÉTRICA; PÁTIO GOURMET (LOJAS); SANTO REMÉDIO; TUBOAÇOS</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Sem conexão</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Twitter/X Ads</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Analista da conta</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Levantar ID da conta e decidir se entra no escopo</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E26" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>PÁTIO GOURMET (LOJAS)</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Sem conexão</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18343,7 +23647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -18449,25 +23753,25 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Analista da conta</t>
+          <t>Analista Inbound (Joyce) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Tarefa no VJOB para o analista</t>
+          <t>E-mail + tarefa no VJOB</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Levantar ID da conta e decidir se entra no escopo (10)</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted (11)</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -18479,25 +23783,25 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Admin do BM Meta (atribuição) + Jussara (OAuth)</t>
+          <t>Analista da conta</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>E-mail + tarefa no VJOB</t>
+          <t>Tarefa no VJOB para o analista</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Concluir atribuição do termo e então autorizar o OAuth (8)</t>
+          <t>Levantar ID da conta e decidir se entra no escopo (10)</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -18509,7 +23813,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Jussara + administrador do MCC</t>
+          <t>Admin do BM Meta (atribuição) + Jussara (OAuth)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -18519,15 +23823,15 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Não integrar; solicitar desvínculo da conta do MCC (5)</t>
+          <t>Concluir atribuição do termo e então autorizar o OAuth (8)</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -18539,7 +23843,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Admin do BM Meta + AM</t>
+          <t>Analista Inbound (Juan Carlos) + admin da conta RD do cliente (a confirmar)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -18549,11 +23853,11 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Validar se a conta ainda é necessária; se sim, reativar no Meta (3)</t>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted (8)</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -18569,7 +23873,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>João (confirmar ID) + Administrador do MCC Google Ads 170-443-9246 (a confirmar)</t>
+          <t>Jussara + administrador do MCC</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -18579,15 +23883,15 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Confirmar ID/vínculo da Comac no MCC; depois criar rascunho (1); Confirmar ID/vínculo da Braga Venda Direta no MCC; depois criar rascunho (1)</t>
+          <t>Não integrar; solicitar desvínculo da conta do MCC (5)</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -18599,28 +23903,148 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do cliente (a confirmar)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>E-mail + tarefa no VJOB</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Validar a conta RD, criar rascunho RD Station, OAuth, camada (nome a confirmar), publicar e somar à Trusted (5)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>docs/nekt/solicitacoes-1743-2026-10-13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Admin do BM Meta + AM</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>E-mail + tarefa no VJOB</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Validar se a conta ainda é necessária; se sim, reativar no Meta (3)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>docs/nekt/solicitacoes-1743-2026-10-13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>João (confirmar ID) + Administrador do MCC Google Ads 170-443-9246 (a confirmar)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>E-mail + tarefa no VJOB</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Confirmar ID/vínculo da Comac no MCC; depois criar rascunho (1); Confirmar ID/vínculo da Braga Venda Direta no MCC; depois criar rascunho (1)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>docs/nekt/solicitacoes-1743-2026-10-13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>Suporte Nekt + admin do BM Meta</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>E-mail + tarefa no VJOB</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Pedir restauração ao suporte e re-autorizar com usuário que tenha a conta (1)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>docs/nekt/solicitacoes-1743-2026-10-13.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Analista Inbound (Bryan) + admin da conta RD do CDL</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>E-mail + tarefa no VJOB</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Conferir plano/permissão da conta RD do CDL e reautorizar (1)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>docs/nekt/solicitacoes-1743-2026-10-13.md</t>
         </is>
@@ -18637,7 +24061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -18709,6 +24133,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>• RD Station: o inventário parte da aba ANALISTAS INBOUND da planilha de squad (51 clientes, plano do RD e analista) cruzada com as 34 fontes rd-station da Nekt, pela descrição da fonte ("BD - RD STATION - &lt;cliente&gt;"). O RD não tem ID de conta nos documentos; a coluna ID fica "—" e a fonte vai na coluna "Fonte / rascunho Nekt". Quem é o analista de cada bloco foi lido do cabeçalho acima da lista de clientes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>• RD Station, contatos e conversões: números da carga de 13/10 (trs_rd_station__contato e __conversao). Uma fonte pode atender mais de uma unidade do cliente; por isso 8 clientes aparecem como "a validar".</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>• Candidatas a não manter (validar com o AM): Don Watches conta 1 (sem atividade desde 2023), Dr. Cabral conta 1 após integrar a nova (0 linhas de desempenho), Santo Remédio VNG (conta saiu do MCC), contas Meta desabilitadas (Santo Remédio Reserva Nova, Dr. Cabral, Millennium Shopping).</t>
         </is>
       </c>
